--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.870490603156</v>
+        <v>7.12895472301285</v>
       </c>
       <c r="D2" t="n">
-        <v>43.75384415087805</v>
+        <v>7.109999674517683</v>
       </c>
       <c r="E2" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F2" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.12754877456234</v>
+        <v>10.90822667586638</v>
       </c>
       <c r="D3" t="n">
-        <v>67.07447731733646</v>
+        <v>10.89960256406717</v>
       </c>
       <c r="E3" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F3" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.20622969742798</v>
+        <v>6.208512325832046</v>
       </c>
       <c r="D4" t="n">
-        <v>38.15486283579335</v>
+        <v>6.200165210816419</v>
       </c>
       <c r="E4" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F4" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.058634292228</v>
+        <v>4.39702807248705</v>
       </c>
       <c r="D5" t="n">
-        <v>27.00960689022785</v>
+        <v>4.389061119662026</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F5" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.52265192056764</v>
+        <v>4.309930937092242</v>
       </c>
       <c r="D6" t="n">
-        <v>26.40138075214424</v>
+        <v>4.290224372223439</v>
       </c>
       <c r="E6" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F6" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.38016070796597</v>
+        <v>4.93677611504447</v>
       </c>
       <c r="D7" t="n">
-        <v>30.31707783014019</v>
+        <v>4.926525147397782</v>
       </c>
       <c r="E7" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F7" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.1689613053772</v>
+        <v>8.964956212123795</v>
       </c>
       <c r="D8" t="n">
-        <v>55.35264986075846</v>
+        <v>8.994805602373249</v>
       </c>
       <c r="E8" t="n">
-        <v>14.22239144822834</v>
+        <v>2.311138610337105</v>
       </c>
       <c r="F8" t="n">
-        <v>14.26468817141643</v>
+        <v>2.318011827855169</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
